--- a/260322/test0322.xlsx
+++ b/260322/test0322.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lienrueiyu/Desktop/LAB/03collegeproject/01Matlab/260322/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59F001B2-010E-D94F-A4E3-CE2CA587212C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88455BE-F90B-9440-AB21-383CAEC71F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19800" xr2:uid="{9222699D-FE95-5345-ACB2-964E3AB48AD8}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -116,6 +116,11 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -140,9 +145,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,7 +536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" ht="16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -537,41 +548,41 @@
       </c>
       <c r="D2">
         <f>(F2*G2*H2)^(1/3)</f>
-        <v>1.2599210498948732</v>
+        <v>7.6725503823575009E-3</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2" si="0">AVERAGE(F2:H2)</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>315</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>45</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>7.986666666666668E-3</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1.1050000000000001E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>7.345E-3</v>
+      </c>
+      <c r="H2" s="1">
+        <v>5.5649999999999996E-3</v>
+      </c>
+      <c r="I2" s="2">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="J2" s="2">
+        <v>41.9</v>
+      </c>
+      <c r="K2" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="L2" s="2">
+        <v>38.1</v>
+      </c>
+      <c r="M2" s="2">
+        <v>270.5</v>
+      </c>
+      <c r="N2" s="2">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16">
       <c r="A3">
         <v>1</v>
       </c>
@@ -583,41 +594,41 @@
       </c>
       <c r="D3">
         <f>(F3*G3*H3)^(1/3)</f>
-        <v>1.2599210498948732</v>
+        <v>9.5883803566435988E-3</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E9" si="1">AVERAGE(F3:H3)</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>315</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>45</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>1.0015666666666666E-2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1.4069999999999999E-2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>9.0670000000000004E-3</v>
+      </c>
+      <c r="H3" s="1">
+        <v>6.9100000000000003E-3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>155.6</v>
+      </c>
+      <c r="J3" s="2">
+        <v>42.1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>26.4</v>
+      </c>
+      <c r="L3" s="2">
+        <v>34.9</v>
+      </c>
+      <c r="M3" s="2">
+        <v>274.5</v>
+      </c>
+      <c r="N3" s="2">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16">
       <c r="A4">
         <v>1</v>
       </c>
@@ -629,41 +640,41 @@
       </c>
       <c r="D4">
         <f>(F4*G4*H4)^(1/3)</f>
-        <v>1.2599210498948732</v>
+        <v>5.9073667178321321E-3</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>315</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>45</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>6.1469999999999997E-3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>8.4659999999999996E-3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5.7120000000000001E-3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4.2630000000000003E-3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="J4" s="2">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="K4" s="2">
+        <v>26.6</v>
+      </c>
+      <c r="L4" s="2">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="M4" s="2">
+        <v>272</v>
+      </c>
+      <c r="N4" s="2">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16">
       <c r="A5">
         <v>1</v>
       </c>
@@ -675,38 +686,38 @@
       </c>
       <c r="D5">
         <f>(F5*G5*H5)^(1/3)</f>
-        <v>1.2599210498948732</v>
+        <v>5.5509759831531792E-3</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>315</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>45</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>90</v>
+        <v>5.730666666666666E-3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>7.698E-3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5.3080000000000002E-3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4.1859999999999996E-3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>155.5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="K5" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="L5" s="2">
+        <v>38</v>
+      </c>
+      <c r="M5" s="2">
+        <v>271.3</v>
+      </c>
+      <c r="N5" s="2">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:14">
